--- a/data/trans_dic/P19D_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P19D_R-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,01%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,18</t>
+          <t>10,48; 15,3</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>23,49; 29,57</t>
+          <t>23,46; 29,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10,65; 17,01</t>
+          <t>10,7; 17,01</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>14,68; 21,06</t>
+          <t>14,43; 20,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,76; 11,55</t>
+          <t>7,66; 11,57</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>13,42; 17,78</t>
+          <t>13,19; 17,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>10,35; 15,99</t>
+          <t>10,19; 15,54</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,15; 14,9</t>
+          <t>9,97; 13,62</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>9,36; 12,59</t>
+          <t>9,48; 12,51</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>18,15; 21,72</t>
+          <t>18,11; 21,85</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,22; 15,4</t>
+          <t>11,08; 15,38</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,61; 16,23</t>
+          <t>12,53; 15,63</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>4,38; 6,96</t>
+          <t>4,36; 6,98</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>8,73; 11,73</t>
+          <t>8,79; 11,98</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8,52; 11,55</t>
+          <t>8,56; 11,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7,18; 38,96</t>
+          <t>6,67; 9,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,74; 7,23</t>
+          <t>4,77; 7,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,95; 11,0</t>
+          <t>7,81; 10,96</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,49; 10,12</t>
+          <t>7,39; 10,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,8; 5,01</t>
+          <t>4,1; 5,78</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4,91; 6,71</t>
+          <t>4,9; 6,67</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8,75; 10,87</t>
+          <t>8,78; 10,81</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8,39; 10,42</t>
+          <t>8,36; 10,36</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,35; 27,48</t>
+          <t>5,72; 7,49</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,7</t>
+          <t>1,68; 5,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,88</t>
+          <t>1,73; 5,67</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,88</t>
+          <t>1,54; 4,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1,48; 4,38</t>
+          <t>1,92; 5,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,74</t>
+          <t>1,54; 5,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,57</t>
+          <t>2,99; 7,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 6,63</t>
+          <t>2,98; 6,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,49</t>
+          <t>1,29; 3,24</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,55</t>
+          <t>1,88; 4,5</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,86; 5,84</t>
+          <t>2,8; 5,74</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,63; 5,0</t>
+          <t>2,69; 5,21</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1,7; 3,5</t>
+          <t>1,95; 3,8</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>5,34%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>7,14%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>6,16; 8,27</t>
+          <t>6,27; 8,31</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>12,41; 14,92</t>
+          <t>12,31; 14,9</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 10,48</t>
+          <t>8,27; 10,44</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7,74; 34,72</t>
+          <t>7,46; 9,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,82; 7,72</t>
+          <t>5,82; 7,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,11</t>
+          <t>9,86; 12,1</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,9; 10,08</t>
+          <t>7,89; 10,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4,4; 6,22</t>
+          <t>5,21; 6,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6,3; 7,66</t>
+          <t>6,22; 7,69</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 13,11</t>
+          <t>11,3; 12,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8,35; 9,84</t>
+          <t>8,26; 9,91</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 21,89</t>
+          <t>6,54; 7,73</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>83745</t>
+          <t>92791</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>87714</t>
+          <t>92452</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>171459</t>
+          <t>185244</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>74036; 111651</t>
+          <t>72368; 105622</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>183254; 230734</t>
+          <t>183048; 231899</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>48702; 77818</t>
+          <t>48965; 77787</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>70967; 101799</t>
+          <t>77381; 110409</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>74376; 110718</t>
+          <t>73431; 110993</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>151520; 200764</t>
+          <t>148928; 199063</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66019; 101947</t>
+          <t>64951; 99103</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>73539; 107974</t>
+          <t>78417; 107096</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>154309; 207682</t>
+          <t>156364; 206325</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>346611; 414720</t>
+          <t>345923; 417216</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>122914; 168641</t>
+          <t>121330; 168418</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>152265; 195964</t>
+          <t>165682; 206736</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>398437</t>
+          <t>173735</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>88281</t>
+          <t>102959</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>486718</t>
+          <t>276693</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>57609; 91430</t>
+          <t>57366; 91811</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>146976; 197497</t>
+          <t>147952; 201719</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>144466; 195851</t>
+          <t>145159; 196697</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160102; 869421</t>
+          <t>143133; 204392</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65038; 99295</t>
+          <t>65569; 100387</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>126191; 174612</t>
+          <t>123921; 173897</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>127959; 172943</t>
+          <t>126348; 174832</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>61599; 110065</t>
+          <t>86393; 121979</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>131863; 180263</t>
+          <t>131609; 179210</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>286049; 355367</t>
+          <t>287066; 353531</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>285592; 354673</t>
+          <t>284705; 352587</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>237042; 1217147</t>
+          <t>243540; 318685</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17255</t>
+          <t>22654</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>15878</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>32036</t>
+          <t>38532</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8202; 25772</t>
+          <t>7592; 25374</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8472; 25803</t>
+          <t>7609; 24902</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8170; 24306</t>
+          <t>7681; 23410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9368; 27679</t>
+          <t>13501; 38345</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>6448; 19370</t>
+          <t>6277; 20843</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>13171; 31999</t>
+          <t>12633; 29906</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14531; 33696</t>
+          <t>15147; 34503</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8713; 22796</t>
+          <t>9355; 23544</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>17417; 39159</t>
+          <t>16181; 38727</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>24673; 50305</t>
+          <t>24157; 49456</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>26429; 50317</t>
+          <t>27082; 52493</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>21826; 45021</t>
+          <t>27856; 54257</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>499437</t>
+          <t>289180</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>190775</t>
+          <t>211289</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>690212</t>
+          <t>500469</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>151457; 203230</t>
+          <t>154159; 204118</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>360147; 432925</t>
+          <t>357212; 432433</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>217086; 277820</t>
+          <t>219393; 276911</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>259073; 1161880</t>
+          <t>252612; 327406</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>159488; 211701</t>
+          <t>159527; 212697</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>309073; 380267</t>
+          <t>309521; 379838</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>225656; 287661</t>
+          <t>225347; 286693</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>157463; 222211</t>
+          <t>188765; 238456</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>327531; 397914</t>
+          <t>323118; 399839</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>683640; 792219</t>
+          <t>682916; 784398</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>459899; 541733</t>
+          <t>454943; 545444</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>442909; 1515124</t>
+          <t>458658; 541857</t>
         </is>
       </c>
     </row>
